--- a/data/trans_orig/IMC_inf_MED_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R2-Edad-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -729,67 +729,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>14224</v>
+        <v>15111</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>9973</v>
+        <v>10091</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>18071</v>
+        <v>19497</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5402623576903324</v>
+        <v>0.4367053078668813</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.3787841147387206</v>
+        <v>0.2916149029298357</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.6863751964660718</v>
+        <v>0.5634357602668972</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>18051</v>
+        <v>23385</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>13449</v>
+        <v>18444</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>21971</v>
+        <v>28441</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5831012649919657</v>
+        <v>0.5675937061756184</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.4344513909415435</v>
+        <v>0.4476510761806652</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.7097372292513752</v>
+        <v>0.6902969068528363</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>32275</v>
+        <v>38497</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>25827</v>
+        <v>31689</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>38011</v>
+        <v>45781</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.5634127523273292</v>
+        <v>0.5078455997807187</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.4508428306117745</v>
+        <v>0.4180353936721968</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.6635486798627775</v>
+        <v>0.6039411093178538</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>12104</v>
+        <v>19492</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>8257</v>
+        <v>15106</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>16355</v>
+        <v>24512</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.4597376423096676</v>
+        <v>0.5632946921331187</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.3136248035339281</v>
+        <v>0.436564239733103</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.6212158852612794</v>
+        <v>0.7083850970701643</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>12906</v>
+        <v>17816</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>8986</v>
+        <v>12760</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>17508</v>
+        <v>22757</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4168987350080343</v>
+        <v>0.4324062938243815</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.2902627707486248</v>
+        <v>0.3097030931471638</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5655486090584564</v>
+        <v>0.5523489238193348</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>25010</v>
+        <v>37307</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>19274</v>
+        <v>30023</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>31458</v>
+        <v>44115</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.4365872476726708</v>
+        <v>0.4921544002192813</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.3364513201372223</v>
+        <v>0.3960588906821461</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.5491571693882249</v>
+        <v>0.5819646063278032</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>26328</v>
+        <v>34603</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>26328</v>
+        <v>34603</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>26328</v>
+        <v>34603</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>30957</v>
+        <v>41201</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>30957</v>
+        <v>41201</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>30957</v>
+        <v>41201</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>57285</v>
+        <v>75804</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>57285</v>
+        <v>75804</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>57285</v>
+        <v>75804</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>131195</v>
+        <v>153467</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>118236</v>
+        <v>139546</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>142422</v>
+        <v>166504</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.6288601103688418</v>
+        <v>0.5968208640121002</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.5667410681351982</v>
+        <v>0.5426853904684834</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.6826721409526995</v>
+        <v>0.6475220780930443</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>96295</v>
+        <v>115817</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>85169</v>
+        <v>103184</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>107326</v>
+        <v>127650</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5112107764370339</v>
+        <v>0.5092527518596922</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4521443141743338</v>
+        <v>0.4537065731130308</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5697746108050366</v>
+        <v>0.5612822954422387</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>320</v>
+        <v>378</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>227490</v>
+        <v>269284</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>210410</v>
+        <v>251938</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>244054</v>
+        <v>287852</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.5730371096170376</v>
+        <v>0.5557217943232319</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.530014118219755</v>
+        <v>0.5199249534003878</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.6147598761276821</v>
+        <v>0.594040560811091</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>77429</v>
+        <v>103673</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>66202</v>
+        <v>90636</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>90388</v>
+        <v>117594</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.3711398896311582</v>
+        <v>0.4031791359878998</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.317327859047301</v>
+        <v>0.3524779219069557</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.4332589318648022</v>
+        <v>0.4573146095315165</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>92071</v>
+        <v>111608</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>81040</v>
+        <v>99775</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>103197</v>
+        <v>124241</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.4887892235629661</v>
+        <v>0.4907472481403077</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.4302253891949635</v>
+        <v>0.4387177045577613</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.5478556858256665</v>
+        <v>0.5462934268869692</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>241</v>
+        <v>306</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>169500</v>
+        <v>215282</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>152936</v>
+        <v>196714</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>186580</v>
+        <v>232628</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.4269628903829624</v>
+        <v>0.4442782056767681</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.3852401238723176</v>
+        <v>0.405959439188909</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.4699858817802448</v>
+        <v>0.480075046599612</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>291</v>
+        <v>358</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>208624</v>
+        <v>257140</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>208624</v>
+        <v>257140</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>208624</v>
+        <v>257140</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>270</v>
+        <v>326</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>188366</v>
+        <v>227425</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>188366</v>
+        <v>227425</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>188366</v>
+        <v>227425</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>561</v>
+        <v>684</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>396990</v>
+        <v>484566</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>396990</v>
+        <v>484566</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>396990</v>
+        <v>484566</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1163,67 +1163,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>71608</v>
+        <v>85851</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>61641</v>
+        <v>76082</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>80312</v>
+        <v>95690</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.534667578987721</v>
+        <v>0.5441022278523743</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.4602493471532809</v>
+        <v>0.4821908638852258</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.5996600757999111</v>
+        <v>0.6064626716361204</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>70781</v>
+        <v>79676</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>60720</v>
+        <v>69504</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>80224</v>
+        <v>89980</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.5364489709032121</v>
+        <v>0.510006448213856</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.4601927905471597</v>
+        <v>0.4448999241713019</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.6080167820673635</v>
+        <v>0.575966809400885</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>142389</v>
+        <v>165526</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>129514</v>
+        <v>151525</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>156454</v>
+        <v>180461</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.5355516198881444</v>
+        <v>0.527138989462073</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.4871237031648518</v>
+        <v>0.4825485366057491</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.5884521501003348</v>
+        <v>0.5747003763205749</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>62322</v>
+        <v>71933</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>53618</v>
+        <v>62094</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>72289</v>
+        <v>81702</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.4653324210122791</v>
+        <v>0.4558977721476257</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.4003399242000886</v>
+        <v>0.3935373283638794</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.5397506528467187</v>
+        <v>0.5178091361147742</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>61163</v>
+        <v>76549</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>51720</v>
+        <v>66245</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>71224</v>
+        <v>86721</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.4635510290967879</v>
+        <v>0.489993551786144</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.3919832179326365</v>
+        <v>0.424033190599115</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.5398072094528402</v>
+        <v>0.555100075828698</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>123485</v>
+        <v>148483</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>109420</v>
+        <v>133548</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>136360</v>
+        <v>162484</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.4644483801118556</v>
+        <v>0.472861010537927</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.4115478498996651</v>
+        <v>0.4252996236794251</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.5128762968351482</v>
+        <v>0.5174514633942509</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>133930</v>
+        <v>157784</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>133930</v>
+        <v>157784</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>133930</v>
+        <v>157784</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>131944</v>
+        <v>156225</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>131944</v>
+        <v>156225</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>131944</v>
+        <v>156225</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>382</v>
+        <v>449</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>265874</v>
+        <v>314009</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>265874</v>
+        <v>314009</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>265874</v>
+        <v>314009</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>63889</v>
+        <v>70651</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>54787</v>
+        <v>60315</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>75368</v>
+        <v>81026</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4139178008601011</v>
+        <v>0.4006537530135227</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3549453618007793</v>
+        <v>0.3420401042836548</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4882833008438157</v>
+        <v>0.4594888676858229</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>40387</v>
+        <v>48273</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>31483</v>
+        <v>39259</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>49982</v>
+        <v>58412</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2703226782299903</v>
+        <v>0.2817457552615616</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2107227455289064</v>
+        <v>0.2291313734646966</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3345426449121877</v>
+        <v>0.3409178157791968</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>104276</v>
+        <v>118924</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>90485</v>
+        <v>104775</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>117460</v>
+        <v>134597</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.3432900973602649</v>
+        <v>0.3420550545213199</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2978888176879267</v>
+        <v>0.3013579347050922</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.386694555624209</v>
+        <v>0.3871340243776084</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>90463</v>
+        <v>105688</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>78984</v>
+        <v>95313</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>99565</v>
+        <v>116024</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.5860821991398989</v>
+        <v>0.5993462469864773</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.5117166991561845</v>
+        <v>0.540511132314177</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.6450546381992207</v>
+        <v>0.6579598957163452</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>109016</v>
+        <v>123064</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>99421</v>
+        <v>112925</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>117920</v>
+        <v>132078</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7296773217700097</v>
+        <v>0.7182542447384384</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6654573550878123</v>
+        <v>0.6590821842208031</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7892772544710934</v>
+        <v>0.770868626535303</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>287</v>
+        <v>330</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>199479</v>
+        <v>228751</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>186295</v>
+        <v>213078</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>213270</v>
+        <v>242900</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6567099026397351</v>
+        <v>0.6579449454786801</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.613305444375791</v>
+        <v>0.6128659756223916</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7021111823120734</v>
+        <v>0.698642065294908</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>154352</v>
+        <v>176339</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>154352</v>
+        <v>176339</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>154352</v>
+        <v>176339</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>149403</v>
+        <v>171337</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>149403</v>
+        <v>171337</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>149403</v>
+        <v>171337</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>440</v>
+        <v>503</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>303755</v>
+        <v>347675</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>303755</v>
+        <v>347675</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>303755</v>
+        <v>347675</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1597,67 +1597,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>280916</v>
+        <v>325079</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>262560</v>
+        <v>303500</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>301398</v>
+        <v>345372</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.5368847747166713</v>
+        <v>0.5194073618784171</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.5018018298204001</v>
+        <v>0.4849276368679208</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.5760283859890361</v>
+        <v>0.5518300341758322</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>225514</v>
+        <v>267151</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>207320</v>
+        <v>246596</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>244101</v>
+        <v>287286</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4504246060940044</v>
+        <v>0.4480993812094337</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.4140860597102639</v>
+        <v>0.4136218620576</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.4875489171772106</v>
+        <v>0.4818713526649803</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>725</v>
+        <v>843</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>506430</v>
+        <v>592231</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>481200</v>
+        <v>564377</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>532083</v>
+        <v>621068</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.4946073589230291</v>
+        <v>0.4846192482017541</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.4699657488694993</v>
+        <v>0.4618263964367272</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.5196611328841555</v>
+        <v>0.5082161603494973</v>
       </c>
     </row>
     <row r="17">
@@ -1668,67 +1668,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>349</v>
+        <v>434</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>242318</v>
+        <v>300787</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>221836</v>
+        <v>280494</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>260674</v>
+        <v>322366</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.4631152252833288</v>
+        <v>0.4805926381215829</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.423971614010964</v>
+        <v>0.448169965824168</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.4981981701795999</v>
+        <v>0.5150723631320794</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>396</v>
+        <v>473</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>275156</v>
+        <v>329037</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>256569</v>
+        <v>308902</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>293350</v>
+        <v>349592</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5495753939059956</v>
+        <v>0.5519006187905663</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5124510828227896</v>
+        <v>0.5181286473350197</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.5859139402897362</v>
+        <v>0.5863781379423997</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>745</v>
+        <v>907</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>517474</v>
+        <v>629823</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>491821</v>
+        <v>600986</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>542704</v>
+        <v>657677</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.5053926410769709</v>
+        <v>0.5153807517982459</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.4803388671158446</v>
+        <v>0.4917838396505027</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.5300342511305007</v>
+        <v>0.5381736035632728</v>
       </c>
     </row>
     <row r="18">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>752</v>
+        <v>896</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -1760,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -1781,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1470</v>
+        <v>1750</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -1862,7 +1862,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2046,67 +2046,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>13879</v>
+        <v>15631</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>9833</v>
+        <v>11466</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>17690</v>
+        <v>20331</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5410854004757066</v>
+        <v>0.507818368460809</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.3833241100611158</v>
+        <v>0.3725129234635024</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.6896356075896365</v>
+        <v>0.6605413912001842</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>13169</v>
+        <v>15209</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>9084</v>
+        <v>11272</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>17912</v>
+        <v>19631</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4711814736004449</v>
+        <v>0.477437054667924</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.3250304471159828</v>
+        <v>0.3538438618181897</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.6409083490116356</v>
+        <v>0.6162453788877985</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>27047</v>
+        <v>30840</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>20901</v>
+        <v>24321</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>32478</v>
+        <v>37236</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.5046356082925827</v>
+        <v>0.4923665970974344</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.3899608352139688</v>
+        <v>0.3882870128188092</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.6059603352661133</v>
+        <v>0.5944850612336808</v>
       </c>
     </row>
     <row r="5">
@@ -2117,67 +2117,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>11772</v>
+        <v>15149</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>7961</v>
+        <v>10449</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>15818</v>
+        <v>19314</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.4589145995242934</v>
+        <v>0.492181631539191</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.3103643924103636</v>
+        <v>0.3394586087998158</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.6166758899388841</v>
+        <v>0.6274870765364976</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>14779</v>
+        <v>16647</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>10036</v>
+        <v>12225</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>18864</v>
+        <v>20584</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5288185263995551</v>
+        <v>0.522562945332076</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3590916509883646</v>
+        <v>0.3837546211122016</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.6749695528840174</v>
+        <v>0.6461561381818102</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>26551</v>
+        <v>31796</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>21120</v>
+        <v>25400</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>32697</v>
+        <v>38315</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.4953643917074173</v>
+        <v>0.5076334029025656</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.3940396647338863</v>
+        <v>0.4055149387663192</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.6100391647860308</v>
+        <v>0.6117129871811907</v>
       </c>
     </row>
     <row r="6">
@@ -2188,16 +2188,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>25651</v>
+        <v>30780</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>25651</v>
+        <v>30780</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>25651</v>
+        <v>30780</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -2209,16 +2209,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>27948</v>
+        <v>31856</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>27948</v>
+        <v>31856</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>27948</v>
+        <v>31856</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -2230,16 +2230,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>53598</v>
+        <v>62636</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>53598</v>
+        <v>62636</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>53598</v>
+        <v>62636</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -2263,67 +2263,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>98871</v>
+        <v>120300</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>87000</v>
+        <v>107714</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>109837</v>
+        <v>134257</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4963501306233004</v>
+        <v>0.4786287378970188</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.4367536402980728</v>
+        <v>0.428552587159933</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5513968575642868</v>
+        <v>0.5341569479902228</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>64246</v>
+        <v>77975</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>54593</v>
+        <v>67258</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>73844</v>
+        <v>88388</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3902326895772182</v>
+        <v>0.3886522192376666</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3316004463793189</v>
+        <v>0.3352361582252018</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.448535810370325</v>
+        <v>0.4405528250287128</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>248</v>
+        <v>302</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>163117</v>
+        <v>198276</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>148256</v>
+        <v>182970</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>178642</v>
+        <v>217568</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4483318971362662</v>
+        <v>0.438688399034185</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4074859156408041</v>
+        <v>0.4048235395980103</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4910031318681566</v>
+        <v>0.481371563348809</v>
       </c>
     </row>
     <row r="8">
@@ -2334,67 +2334,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>147</v>
+        <v>190</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>100326</v>
+        <v>131044</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>89360</v>
+        <v>117087</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>112197</v>
+        <v>143630</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5036498693766996</v>
+        <v>0.5213712621029812</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4486031424357131</v>
+        <v>0.4658430520097769</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.5632463597019272</v>
+        <v>0.5714474128400671</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>100388</v>
+        <v>122655</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>90790</v>
+        <v>112242</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>110041</v>
+        <v>133372</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6097673104227818</v>
+        <v>0.6113477807623334</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5514641896296749</v>
+        <v>0.5594471749712869</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.6683995536206809</v>
+        <v>0.6647638417747983</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>307</v>
+        <v>386</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>200714</v>
+        <v>253699</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>185189</v>
+        <v>234407</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>215575</v>
+        <v>269005</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.5516681028637338</v>
+        <v>0.561311600965815</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.5089968681318436</v>
+        <v>0.5186284366511908</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.5925140843591961</v>
+        <v>0.5951764604019896</v>
       </c>
     </row>
     <row r="9">
@@ -2405,16 +2405,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>295</v>
+        <v>370</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>199197</v>
+        <v>251344</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>199197</v>
+        <v>251344</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>199197</v>
+        <v>251344</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -2426,16 +2426,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>164634</v>
+        <v>200630</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>164634</v>
+        <v>200630</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>164634</v>
+        <v>200630</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -2447,16 +2447,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>555</v>
+        <v>688</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>363831</v>
+        <v>451975</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>363831</v>
+        <v>451975</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>363831</v>
+        <v>451975</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -2480,67 +2480,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>78130</v>
+        <v>90823</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>67602</v>
+        <v>79666</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>89148</v>
+        <v>101455</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.5097998626875803</v>
+        <v>0.50406793525588</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.4411032422835711</v>
+        <v>0.4421438457337736</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.5816886149112509</v>
+        <v>0.5630746180885317</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>57635</v>
+        <v>66733</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>48056</v>
+        <v>56665</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>67928</v>
+        <v>77682</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3748462438304267</v>
+        <v>0.364178038392152</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3125472354301158</v>
+        <v>0.3092299173279012</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.4417881567747411</v>
+        <v>0.4239273116509774</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>135765</v>
+        <v>157557</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>121404</v>
+        <v>142062</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>150209</v>
+        <v>172429</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.4422133325284838</v>
+        <v>0.4335334917831102</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.3954355192483691</v>
+        <v>0.3908987811766894</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.4892582571827442</v>
+        <v>0.4744557503221206</v>
       </c>
     </row>
     <row r="11">
@@ -2551,67 +2551,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>75127</v>
+        <v>89358</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>64109</v>
+        <v>78726</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>85655</v>
+        <v>100515</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.4902001373124197</v>
+        <v>0.49593206474412</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.418311385088749</v>
+        <v>0.4369253819114683</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.5588967577164288</v>
+        <v>0.5578561542662265</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>96121</v>
+        <v>116511</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>85828</v>
+        <v>105562</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>105700</v>
+        <v>126579</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.6251537561695732</v>
+        <v>0.635821961607848</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.5582118432252592</v>
+        <v>0.5760726883490227</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6874527645698842</v>
+        <v>0.6907700826720987</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>244</v>
+        <v>295</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>171248</v>
+        <v>205868</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>156804</v>
+        <v>190996</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>185609</v>
+        <v>221363</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.5577866674715162</v>
+        <v>0.5664665082168898</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.5107417428172558</v>
+        <v>0.5255442496778795</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.6045644807516309</v>
+        <v>0.6091012188233108</v>
       </c>
     </row>
     <row r="12">
@@ -2622,16 +2622,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>153257</v>
+        <v>180181</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>153257</v>
+        <v>180181</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>153257</v>
+        <v>180181</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -2643,16 +2643,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>153756</v>
+        <v>183244</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>153756</v>
+        <v>183244</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>153756</v>
+        <v>183244</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -2664,16 +2664,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>433</v>
+        <v>515</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>307013</v>
+        <v>363425</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>307013</v>
+        <v>363425</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>307013</v>
+        <v>363425</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -2697,67 +2697,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>46920</v>
+        <v>57306</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>37403</v>
+        <v>47053</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>57043</v>
+        <v>68435</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.3211120151703006</v>
+        <v>0.3386983661031804</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2559771706121987</v>
+        <v>0.2781004603864018</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.390391675973446</v>
+        <v>0.4044734198855709</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>34437</v>
+        <v>37010</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>26738</v>
+        <v>28156</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>42635</v>
+        <v>46244</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2444767858635145</v>
+        <v>0.2287944436990382</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.189820460673078</v>
+        <v>0.1740608062636012</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3026747272513188</v>
+        <v>0.2858754019113036</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>81357</v>
+        <v>94317</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>69738</v>
+        <v>79842</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>93924</v>
+        <v>109128</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2834960334322737</v>
+        <v>0.2849806945216043</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2430098094074735</v>
+        <v>0.2412449342065583</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3272868806366763</v>
+        <v>0.3297323258102711</v>
       </c>
     </row>
     <row r="14">
@@ -2768,67 +2768,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>99197</v>
+        <v>111890</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>89074</v>
+        <v>100761</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>108714</v>
+        <v>122143</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.6788879848296995</v>
+        <v>0.6613016338968196</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6096083240265541</v>
+        <v>0.5955265801144293</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7440228293878013</v>
+        <v>0.7218995396135987</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>106425</v>
+        <v>124752</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>98227</v>
+        <v>115518</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>114124</v>
+        <v>133606</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7555232141364855</v>
+        <v>0.7712055563009618</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6973252727486813</v>
+        <v>0.7141245980886963</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8101795393269221</v>
+        <v>0.8259391937363987</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>287</v>
+        <v>330</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>205621</v>
+        <v>236641</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>193054</v>
+        <v>221830</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>217240</v>
+        <v>251116</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7165039665677263</v>
+        <v>0.7150193054783958</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6727131193633239</v>
+        <v>0.6702676741897284</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7569901905925265</v>
+        <v>0.7587550657934417</v>
       </c>
     </row>
     <row r="15">
@@ -2839,16 +2839,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>146117</v>
+        <v>169196</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>146117</v>
+        <v>169196</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>146117</v>
+        <v>169196</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -2860,16 +2860,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>140862</v>
+        <v>161762</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>140862</v>
+        <v>161762</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>140862</v>
+        <v>161762</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -2881,16 +2881,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>398</v>
+        <v>459</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>286978</v>
+        <v>330958</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>286978</v>
+        <v>330958</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>286978</v>
+        <v>330958</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -2914,67 +2914,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>237801</v>
+        <v>284061</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>219700</v>
+        <v>262329</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>256707</v>
+        <v>303976</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.4536268504821084</v>
+        <v>0.4498187677890572</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.4190984251942523</v>
+        <v>0.4154058591283558</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.4896927445480223</v>
+        <v>0.4813556038517585</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>169486</v>
+        <v>196928</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>152738</v>
+        <v>178772</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>185334</v>
+        <v>214860</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.3478785913841982</v>
+        <v>0.3410060676206463</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3135019948392222</v>
+        <v>0.3095667519334427</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.3804068958485285</v>
+        <v>0.3720579677346967</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>590</v>
+        <v>699</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>407287</v>
+        <v>480989</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>380987</v>
+        <v>452108</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>433598</v>
+        <v>507410</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.4026881249815326</v>
+        <v>0.3978428558400455</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.3766850554496688</v>
+        <v>0.3739540851910583</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.4287020752950155</v>
+        <v>0.4196961487405965</v>
       </c>
     </row>
     <row r="17">
@@ -2985,67 +2985,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>407</v>
+        <v>493</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>286420</v>
+        <v>347439</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>267514</v>
+        <v>327524</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>304521</v>
+        <v>369171</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.5463731495178916</v>
+        <v>0.5501812322109428</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.510307255451978</v>
+        <v>0.5186443961482414</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.5809015748057479</v>
+        <v>0.5845941408716442</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>474</v>
+        <v>569</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>317713</v>
+        <v>380564</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>301865</v>
+        <v>362632</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>334461</v>
+        <v>398720</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.6521214086158018</v>
+        <v>0.6589939323793537</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6195931041514716</v>
+        <v>0.6279420322653032</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.6864980051607779</v>
+        <v>0.6904332480665573</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>881</v>
+        <v>1062</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>604134</v>
+        <v>728004</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>577823</v>
+        <v>701583</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>630434</v>
+        <v>756885</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.5973118750184674</v>
+        <v>0.6021571441599545</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.5712979247049845</v>
+        <v>0.5803038512594035</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.6233149445503311</v>
+        <v>0.626045914808942</v>
       </c>
     </row>
     <row r="18">
@@ -3056,16 +3056,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>745</v>
+        <v>897</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -3077,16 +3077,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>726</v>
+        <v>864</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -3098,16 +3098,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1471</v>
+        <v>1761</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -3179,7 +3179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3580,67 +3580,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>34801</v>
+        <v>35714</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>28546</v>
+        <v>29333</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>42049</v>
+        <v>42763</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4975666117257556</v>
+        <v>0.4907691539336634</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.4081452781520847</v>
+        <v>0.4030774872697264</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.6011987306704191</v>
+        <v>0.5876261818821004</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>20654</v>
+        <v>22649</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>15707</v>
+        <v>17722</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>26580</v>
+        <v>27988</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4038599361124355</v>
+        <v>0.417348406910227</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3071271958719704</v>
+        <v>0.3265675048788706</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5197318640812608</v>
+        <v>0.5157426440261176</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>55455</v>
+        <v>58363</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>47078</v>
+        <v>49635</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>63832</v>
+        <v>67666</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4579881086804841</v>
+        <v>0.4594059959909861</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.3888055639513798</v>
+        <v>0.3907040039943658</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.5271722607045563</v>
+        <v>0.5326361099706399</v>
       </c>
     </row>
     <row r="8">
@@ -3651,67 +3651,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>35141</v>
+        <v>37058</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>27893</v>
+        <v>30009</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>41396</v>
+        <v>43439</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5024333882742446</v>
+        <v>0.5092308460663367</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3988012693295809</v>
+        <v>0.4123738181178997</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.5918547218479151</v>
+        <v>0.5969225127302736</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>30488</v>
+        <v>31619</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>24562</v>
+        <v>26280</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>35435</v>
+        <v>36546</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5961400638875644</v>
+        <v>0.5826515930897732</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.480268135918739</v>
+        <v>0.4842573559738825</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.6928728041280298</v>
+        <v>0.6734324951211291</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>65629</v>
+        <v>68677</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>57252</v>
+        <v>59374</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>74006</v>
+        <v>77405</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.542011891319516</v>
+        <v>0.5405940040090139</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.4728277392954439</v>
+        <v>0.46736389002936</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.6111944360486202</v>
+        <v>0.6092959960056337</v>
       </c>
     </row>
     <row r="9">
@@ -3722,16 +3722,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>69942</v>
+        <v>72772</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>69942</v>
+        <v>72772</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>69942</v>
+        <v>72772</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3743,16 +3743,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>51142</v>
+        <v>54268</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>51142</v>
+        <v>54268</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>51142</v>
+        <v>54268</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3764,16 +3764,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>121084</v>
+        <v>127040</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>121084</v>
+        <v>127040</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>121084</v>
+        <v>127040</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3797,67 +3797,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>41987</v>
+        <v>44618</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>33389</v>
+        <v>35655</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>51833</v>
+        <v>54027</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.4512007743410978</v>
+        <v>0.4492666121698651</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.3588018948315005</v>
+        <v>0.3590238620686925</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.5569988757886388</v>
+        <v>0.5440154245409522</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>26386</v>
+        <v>29792</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>19761</v>
+        <v>22710</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>32900</v>
+        <v>37232</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.3819484754500291</v>
+        <v>0.3929672875269292</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2860539199486997</v>
+        <v>0.2995577605800281</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.4762404484601391</v>
+        <v>0.4911068348652348</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>68373</v>
+        <v>74409</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>56957</v>
+        <v>61944</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>79889</v>
+        <v>86426</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.4216946828528128</v>
+        <v>0.4248943244783879</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.3512847681416058</v>
+        <v>0.3537136932658245</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.4927213211580433</v>
+        <v>0.493513373289573</v>
       </c>
     </row>
     <row r="11">
@@ -3868,67 +3868,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>54694</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>45285</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>63657</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0.5507333878301349</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0.4559845754590478</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0.6409761379313077</v>
+      </c>
+      <c r="J11" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>51070</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>41224</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>59668</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0.5487992256589023</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>0.4430011242113603</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>0.6411981051684995</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>58</v>
-      </c>
       <c r="K11" s="5" t="n">
-        <v>42696</v>
+        <v>46020</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>36182</v>
+        <v>38580</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>49321</v>
+        <v>53102</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.6180515245499708</v>
+        <v>0.6070327124730708</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.5237595515398611</v>
+        <v>0.5088931651347655</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7139460800513006</v>
+        <v>0.700442239419972</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>93766</v>
+        <v>100715</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>82250</v>
+        <v>88698</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>105182</v>
+        <v>113180</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.5783053171471872</v>
+        <v>0.5751056755216118</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.5072786788419565</v>
+        <v>0.5064866267104274</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.6487152318583936</v>
+        <v>0.6462863067341756</v>
       </c>
     </row>
     <row r="12">
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>93057</v>
+        <v>99312</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>93057</v>
+        <v>99312</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>93057</v>
+        <v>99312</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3960,16 +3960,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>69082</v>
+        <v>75812</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>69082</v>
+        <v>75812</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>69082</v>
+        <v>75812</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3981,16 +3981,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>162139</v>
+        <v>175124</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>162139</v>
+        <v>175124</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>162139</v>
+        <v>175124</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -4014,67 +4014,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>40245</v>
+        <v>42647</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>30288</v>
+        <v>32357</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>51863</v>
+        <v>54656</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.3234074493580646</v>
+        <v>0.3281437830052117</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.243396173226718</v>
+        <v>0.2489695411634774</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4167749080016044</v>
+        <v>0.4205504678136447</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>21</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>15268</v>
+        <v>15269</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>9760</v>
+        <v>10013</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>22623</v>
+        <v>22945</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1476843742340614</v>
+        <v>0.1441066044189455</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.09439964962801552</v>
+        <v>0.09450059556166344</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2188176780081332</v>
+        <v>0.2165608588327953</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>55513</v>
+        <v>57915</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>43361</v>
+        <v>45922</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>68864</v>
+        <v>72633</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2436654635904065</v>
+        <v>0.2454903606242617</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1903245010039695</v>
+        <v>0.1946559560443031</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3022673912562037</v>
+        <v>0.307876255866775</v>
       </c>
     </row>
     <row r="14">
@@ -4085,67 +4085,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>84195</v>
+        <v>87316</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>72577</v>
+        <v>75307</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>94152</v>
+        <v>97606</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.6765925506419354</v>
+        <v>0.6718562169947884</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.5832250919983956</v>
+        <v>0.5794495321863556</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7566038267732821</v>
+        <v>0.7510304588365225</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>88118</v>
+        <v>90684</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>80763</v>
+        <v>83008</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>93626</v>
+        <v>95940</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8523156257659386</v>
+        <v>0.8558933955810545</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7811823219918668</v>
+        <v>0.7834391411672046</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9056003503719847</v>
+        <v>0.9054994044383365</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>172313</v>
+        <v>178001</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>158962</v>
+        <v>163283</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>184465</v>
+        <v>189994</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7563345364095935</v>
+        <v>0.7545096393757383</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6977326087437963</v>
+        <v>0.6921237441332255</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.8096754989960306</v>
+        <v>0.805344043955697</v>
       </c>
     </row>
     <row r="15">
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>124440</v>
+        <v>129963</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>124440</v>
+        <v>129963</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>124440</v>
+        <v>129963</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -4177,16 +4177,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>103386</v>
+        <v>105953</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>103386</v>
+        <v>105953</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>103386</v>
+        <v>105953</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -4198,16 +4198,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>227826</v>
+        <v>235916</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>227826</v>
+        <v>235916</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>227826</v>
+        <v>235916</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -4231,67 +4231,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>121338</v>
+        <v>127284</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>106201</v>
+        <v>111836</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>137074</v>
+        <v>145071</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.410877839109871</v>
+        <v>0.4106948042901157</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.3596202801771443</v>
+        <v>0.360849822429133</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.4641609216140092</v>
+        <v>0.4680858711282094</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>66080</v>
+        <v>71481</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>54849</v>
+        <v>60288</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>78050</v>
+        <v>84451</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2797420285860966</v>
+        <v>0.2874848544914089</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2321959483809797</v>
+        <v>0.2424683607083414</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.3304118024216539</v>
+        <v>0.339650530879622</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>187419</v>
+        <v>198765</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>167434</v>
+        <v>179250</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>208024</v>
+        <v>218676</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.3525997894573501</v>
+        <v>0.3558486175747382</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.3150023636177863</v>
+        <v>0.3209115726201317</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.3913647415747844</v>
+        <v>0.3914969242414433</v>
       </c>
     </row>
     <row r="17">
@@ -4302,67 +4302,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>173977</v>
+        <v>182639</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>158241</v>
+        <v>164852</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>189114</v>
+        <v>198087</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.589122160890129</v>
+        <v>0.5893051957098844</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.5358390783859908</v>
+        <v>0.53191412887179</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6403797198228557</v>
+        <v>0.6391501775708668</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>170139</v>
+        <v>177161</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>158169</v>
+        <v>164191</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>181370</v>
+        <v>188354</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.7202579714139035</v>
+        <v>0.7125151455085911</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6695881975783458</v>
+        <v>0.6603494691203782</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.7678040516190201</v>
+        <v>0.7575316392916587</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>344115</v>
+        <v>359800</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>323510</v>
+        <v>339889</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>364100</v>
+        <v>379315</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.6474002105426498</v>
+        <v>0.6441513824252617</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.6086352584252156</v>
+        <v>0.6085030757585567</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.6849976363822137</v>
+        <v>0.6790884273798686</v>
       </c>
     </row>
     <row r="18">
@@ -4373,16 +4373,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -4394,16 +4394,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -4415,16 +4415,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
